--- a/QA/LC_TestCase.xlsx
+++ b/QA/LC_TestCase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\전체\학교 과제\2-2학기\LC QA 문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974D7356-63AA-4310-B562-97F86312495B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61383EA-1638-428E-9AF2-6B7935362986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7035" yWindow="2850" windowWidth="23565" windowHeight="17415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCase" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="198">
   <si>
     <t>No</t>
   </si>
@@ -1891,10 +1891,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>로비 화면 UI</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">1. </t>
     </r>
@@ -1996,18 +1992,314 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">설정 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
+      <t>Exit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를 누른다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>사운드 볼륨을 조절한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼룸이 커지거나 작아진다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>N/T</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Exit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버튼을 클릭한다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정 UI가 닫힌다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼륨을 올린다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>볼륨을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내린다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼륨이 커진다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>볼륨이 작아진다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 이름을 입력한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방 이름을 입력한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 이름이 입력된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방 이름이 입력된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방을 생성한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성된 방에 참가한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>LobbyScene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서 실행</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>GameScene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서  실행</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MainScene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서 실행</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MainScene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서 실행 / 설정 UI에서 실행</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임을 시작한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 이름을 입력하지 않고 방을 생성 / 참가 한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방 이름을 입력하지 않고 방을 생성 / 참가 한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>생성된 방에 참가되고 해당 방의 플레이어 리스트가 표시된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방 이름에 맞게 방이 생성되고 해당 방의 플레이어 리스트가 표시된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 방에 참가한 플레이어들이 GameScene으로 진입한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 이름이  랜덤으로 설정되고 방이 생성된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방이 생성되지 않는다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">임시) 유니티 아이콘과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Love Crown </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제못이 뜬다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>PASS</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fail</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Scene </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>별로 사운드가 동일하게 조절되는지 확인한다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainScene, GameScene에서 실행</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BTL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참고</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">인게임 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>UI</t>
@@ -2015,22 +2307,149 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Exit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>를 누른다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>사운드 볼륨을 조절한다</t>
+    <t>모든 텍스트에서 한글 폰트가 정상적으로 나오는지
+확인한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>GameScene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실행</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>폰트가 모두 정상적으로 출력된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">BTL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참고</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 이동 관련</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">UI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관련 보완</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 종료</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임메뉴</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>호감도가 0으로 표시된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 처음 대화 시작 시 호감도가 0으로 표시된다</t>
+    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -2044,50 +2463,333 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>사운드 불륨을 조절하는 슬라이더를 조절한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>볼룸이 커지거나 작아진다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>N/T</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Exit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>버튼을 클릭한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>설정 UI가 닫힌다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>볼륨을 올린다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>볼륨을</t>
+      <t xml:space="preserve">각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 처음으로 대화를 시도
+2.  좌측 상단의 호감도가 0으로 표시되는지 확인</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 Scene에서 동일한 값의 사운드가 출력된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>GameScene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실행</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>로비 화면으로 돌아온다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 대화 중 호감도가 증가하는 선택지를 클릭한다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1. NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 대화를 시도
+2.  대화 중 호감도가 증가하는 선택지를 클릭
+3.  대화 종료</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>정해진 수치만큼 호감도가 증가한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 대화 중 호감도가 감소하는 선택지를 클릭한다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 대화 중 호감도가 불변하는 선택지를 클릭한다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1. NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 대화를 시도
+2.  대화 중 호감도가 감소하는 선택지를 클릭
+3.  대화 종료</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1. NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 대화를 시도
+2.  대화 중 호감도가 불변하는 선택지를 클릭
+3.  대화 종료</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>정해진 수치만큼 호감도가 감소한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>호감도가 증감하지 않는다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">상점에서 호감도 아이템을 구매
+2.  아이템에 맞는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 대화</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방 이름 칸을 비워두고 플레이어 이름만 입력
+2.  해당 방을 생성 / 참가</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플레이어 이름 칸을 비워두고 방 이름만 입력
+2.  해당 방을 생성 / 참가</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">플레이어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">가 이름 및 방 이름을 입력
+2.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>Create Room</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>을</t>
     </r>
     <r>
       <rPr>
@@ -2104,7 +2806,78 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>내린다</t>
+      <t xml:space="preserve">클릭
+3.  플레이어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">가 이름 및 방 이름을 입력
+4.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>Join Room</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">을 클릭
+5.  플레이어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>Game Start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를 클릭</t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2119,7 +2892,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>사운드</t>
+      <t>플레이어</t>
     </r>
     <r>
       <rPr>
@@ -2136,22 +2909,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>슬라이더를 왼쪽으로 조절한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사운드 슬라이더를</t>
+      <t>이름</t>
     </r>
     <r>
       <rPr>
@@ -2168,53 +2926,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>오른쪽으로 조절한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>볼륨이 커진다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>볼륨이 작아진다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어 이름을 입력한다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방 이름을 입력한다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Player Name </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>칸에 숫자 혹은 문자를 입력한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Room Name </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>칸에</t>
+      <t>및</t>
     </r>
     <r>
       <rPr>
@@ -2231,140 +2943,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>숫자 혹은 문자를 입력한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어 이름이 입력된다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방 이름이 입력된다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방을 생성한다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">플레이어 이름 및 방 이름을 입력한다
-2.  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>Create Room</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">을 클릭한다 </t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>생성된 방에 참가한다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>LobbyScene</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에서 실행</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>GameScene</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에서  실행</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>MainScene</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에서 실행</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>MainScene</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에서 실행 / 설정 UI에서 실행</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임을 시작한다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>플레이어</t>
+      <t>방</t>
     </r>
     <r>
       <rPr>
@@ -2381,7 +2960,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>이름</t>
+      <t>이름을</t>
     </r>
     <r>
       <rPr>
@@ -2398,58 +2977,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>및</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>방</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이름을</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>입력한다</t>
+      <t>입력</t>
     </r>
     <r>
       <rPr>
@@ -2484,7 +3012,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>클릭한다</t>
+      <t>클릭</t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2499,24 +3027,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">플레이어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">가 이름 및 방 이름을 입력한다
+      <t xml:space="preserve">플레이어 이름 및 방 이름을 입력
 2.  </t>
     </r>
     <r>
@@ -2534,7 +3045,22 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>을</t>
+      <t>을 클릭</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Room Name </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>칸에</t>
     </r>
     <r>
       <rPr>
@@ -2551,78 +3077,38 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">클릭한다
-3.  플레이어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">가 이름 및 방 이름을 입력한다
-4.  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>Join Room</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">을 클릭한다
-5.  플레이어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">가 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>Game Start</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>를 클릭한다</t>
+      <t>숫자 혹은 문자를 입력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Player Name </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>칸에 숫자 혹은 문자를 입력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1. NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와 대화를 시도
+2.  대화 / 선택지 / 재화 / 호감도 / 아이템 구매 확인창의 한글 텍스트가 정상적으로 출력되는지 확인</t>
     </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2637,17 +3123,59 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>플레이어 이름 칸을 비워두고 방 이름만 입력한다
-2.  해당 방을 생성 / 참가 한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어 이름을 입력하지 않고 방을 생성 / 참가 한다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방 이름을 입력하지 않고 방을 생성 / 참가 한다</t>
+      <t>사운드 불륨을 조절하는 슬라이더를 조절</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1. MainScene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">에서 볼륨을 조정
+2.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>GameScene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">에서 불륨을 조절
+3.  두 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에서 불륨이 동일한지 확인</t>
+    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -2661,69 +3189,74 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>방 이름 칸을 비워두고 플레이어 이름만 입력한다
-2.  해당 방을 생성 / 참가 한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>생성된 방에 참가되고 해당 방의 플레이어 리스트가 표시된다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방 이름에 맞게 방이 생성되고 해당 방의 플레이어 리스트가 표시된다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 방에 참가한 플레이어들이 GameScene으로 진입한다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어 이름이  랜덤으로 설정되고 방이 생성된다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방이 생성되지 않는다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">임시) 유니티 아이콘과 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Love Crown </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>제못이 뜬다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>PASS</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fail</t>
+      <t>사운드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슬라이더를 왼쪽으로 조절</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사운드 슬라이더를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오른쪽으로 조절</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임을 진행
+2.  타이머가 종료된 후 게임 결과 화면이 출력
+3.  로비로 돌아가기 버튼을 클릭</t>
+    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -2741,40 +3274,305 @@
         <sz val="9"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Scene </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>별로 사운드가 동일하게 조절되는지 확인한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1. MainScene</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">에서 볼륨을 조정한다
-2.  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
+        <charset val="129"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에게 할당된 호감도 아이템을 선물한다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">각 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>NPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에게 할당되지 않은 호감도 아이템을 선물한다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상점에서 호감도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이템을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구매</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이템에 맞지 않는 NPC와 대화</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템이 제거되고 호감도가 증가, 감사 전용 대화창이 출력된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템이 제거 및 호감도 증가 X, 거절 전용 대화창이 출력된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>로비 화면</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">게임 결과 화면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>UI</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 결과 화면이 정상적으로 출력되는지 확인한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>진행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>타이머가 끝나고 게임 결과 화면 출력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 결과 화면이 정상적으로 출력된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이머가 끝나면 게임이 종료되고 로비 화면으로 돌아간다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>로비로 돌아간 후 다시 게임을 시작한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임 종료</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후 로비로 돌아가기 클릭
+2.  로비로 돌아온 후 방 생성 및 입장
+3.  게임 시작 버튼 클릭</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>정상적으로 방이 생성/입장되고 게임이 시작된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이머</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이머 UI</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이머가 정상적으로 화면에 출력되는지 확인한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>GameScene</t>
     </r>
     <r>
@@ -2784,92 +3582,6 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve">에서 불륨을 조절한다
-3.  두 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>Scene</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에서 불륨이 동일한지 확인한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainScene, GameScene에서 실행</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>두 Scene에서 동일한 값의 사운드가 난다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">BTL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>참고</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">인게임 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>UI</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 텍스트에서 한글 폰트가 정상적으로 나오는지
-확인한다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t>GameScene</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
       <t>에서</t>
     </r>
     <r>
@@ -2877,6 +3589,7 @@
         <sz val="9"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <charset val="129"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
@@ -2893,6 +3606,67 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방을 생성하고 게임을 시작
+2.  인게임 화면에서 우측 상단에 타이머가 표시되는지 확인</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이머가 정상적으로 출력된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이머의 시간이 정상적으로 줄어드는지 확인한다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>생성 후 게임을 진행
+2.  타이머가 1초씩 줄어드는지 확인</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이머의 시간이 1초씩 정상적으로 줄어든다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t>1. NPC</t>
     </r>
     <r>
@@ -2902,84 +3676,16 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>와 대화를 시도한다
-2.  대화 / 선택지 / 재화 / 호감도 / 아이템 구매 확인창의 한글 텍스트가 정상적으로 출력되는지 확인한다</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>폰트가 모두 정상적으로 출력된다</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">BTL </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="돋움"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>참고</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>퀘스트</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어 이동 관련</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">UI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관련 보완</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>필요</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>타이머 관련</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 종료</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 종료 결과 화면</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임메뉴</t>
+      <t>와 대화 및 아이템을 사용해 호감도를 올린다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>호감도가 일정수치에 도달하면 해당 플레이어에게 귀속된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>호감도가 일정 수치에 도달하면 플레이어에게 귀속된다</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -3257,17 +3963,17 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="medium">
+      <top style="medium">
         <color indexed="64"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3373,13 +4079,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3388,20 +4088,17 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3412,23 +4109,509 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="82">
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9900FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEFEFEF"/>
+          <bgColor rgb="FFEFEFEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9900FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEFEFEF"/>
+          <bgColor rgb="FFEFEFEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9900FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEFEFEF"/>
+          <bgColor rgb="FFEFEFEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9900FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEFEFEF"/>
+          <bgColor rgb="FFEFEFEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9900FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEFEFEF"/>
+          <bgColor rgb="FFEFEFEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9900FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEFEFEF"/>
+          <bgColor rgb="FFEFEFEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9900FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEFEFEF"/>
+          <bgColor rgb="FFEFEFEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF9900"/>
@@ -4184,14 +5367,14 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.42578125" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="59.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="57" bestFit="1" customWidth="1"/>
@@ -4241,10 +5424,10 @@
     </row>
     <row r="2" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
-        <f t="shared" ref="A2:A49" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A58" si="0">ROW()-2</f>
         <v>0</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="48" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="10" t="s">
@@ -4264,7 +5447,7 @@
         <v>33</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
@@ -4278,28 +5461,28 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="38" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38" t="s">
+      <c r="F3" s="47"/>
+      <c r="G3" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="I3" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
+      <c r="H3" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
       <c r="L3" s="10" t="str">
         <f t="shared" si="1"/>
         <v>게임실행</v>
@@ -4310,16 +5493,16 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
       <c r="L4" s="10" t="str">
         <f t="shared" si="1"/>
         <v>게임실행</v>
@@ -4330,26 +5513,26 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="38" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38" t="s">
+      <c r="F5" s="47"/>
+      <c r="G5" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
+      <c r="I5" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
       <c r="L5" s="10" t="str">
         <f t="shared" si="1"/>
         <v>게임실행</v>
@@ -4360,16 +5543,16 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
       <c r="L6" s="10" t="str">
         <f t="shared" si="1"/>
         <v>게임실행</v>
@@ -4380,8 +5563,8 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
       <c r="D7" s="12" t="s">
         <v>22</v>
       </c>
@@ -4396,7 +5579,7 @@
         <v>35</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
@@ -4410,34 +5593,34 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="B8" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>90</v>
+      <c r="C8" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>176</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>87</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13" t="str">
-        <f t="shared" ref="L8:L16" si="2">IF(B8="",L7,B8)</f>
+        <f t="shared" ref="L8:L12" si="2">IF(B8="",L7,B8)</f>
         <v>메뉴기능</v>
       </c>
     </row>
@@ -4446,23 +5629,23 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="42"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="56"/>
       <c r="E9" s="21" t="s">
         <v>88</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
@@ -4476,23 +5659,23 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="42"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="56"/>
       <c r="E10" s="21" t="s">
         <v>89</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
@@ -4506,25 +5689,25 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="39" t="s">
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>100</v>
-      </c>
       <c r="F11" s="10" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
@@ -4538,23 +5721,23 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
       <c r="E12" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
@@ -4568,127 +5751,126 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="33" t="s">
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10" t="str">
-        <f t="shared" si="2"/>
+      <c r="I13" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36" t="str">
+        <f>IF(B13="",L12,B13)</f>
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.2">
       <c r="A14" s="20">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="11" t="str">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36" t="str">
         <f>IF(B14="",L12,B14)</f>
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A15" s="20">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10" t="str">
-        <f>IF(B15="",L12,B15)</f>
+    <row r="15" spans="1:12" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="36"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12" t="str">
+        <f>IF(B15="",L13,B15)</f>
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="20">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v>메뉴기능</v>
+      <c r="B16" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="40" t="str">
+        <f>IF(B16="",#REF!,B16)</f>
+        <v>인게임기능</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
@@ -4696,34 +5878,28 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11" t="str">
-        <f>IF(B17="",#REF!,B17)</f>
+      <c r="B17" s="47"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10" t="str">
+        <f t="shared" ref="L17:L45" si="3">IF(B17="",L16,B17)</f>
         <v>인게임기능</v>
       </c>
     </row>
@@ -4732,53 +5908,53 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="22" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>51</v>
+        <v>74</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>52</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
       <c r="L18" s="10" t="str">
-        <f t="shared" ref="L18:L48" si="3">IF(B18="",L17,B18)</f>
+        <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="27" x14ac:dyDescent="0.2">
       <c r="A19" s="20">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H19" s="21" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
@@ -4792,23 +5968,23 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="22" t="s">
-        <v>53</v>
+      <c r="B20" s="47"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="21" t="s">
+        <v>45</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>55</v>
+        <v>76</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
@@ -4822,23 +5998,23 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="42"/>
       <c r="E21" s="21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>68</v>
+        <v>77</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -4852,23 +6028,23 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
@@ -4882,57 +6058,59 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="21" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H23" s="21" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I23" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="J23" s="10"/>
+        <v>127</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>130</v>
+      </c>
       <c r="K23" s="10"/>
       <c r="L23" s="10" t="str">
         <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A24" s="20">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="53" t="s">
+        <v>60</v>
+      </c>
       <c r="E24" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="21" t="s">
-        <v>57</v>
+        <v>80</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>62</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>144</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="10" t="str">
         <f t="shared" si="3"/>
@@ -4944,25 +6122,23 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>61</v>
+      <c r="B25" s="45"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="22" t="s">
+        <v>63</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I25" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
@@ -4971,28 +6147,28 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="27" x14ac:dyDescent="0.2">
       <c r="A26" s="20">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="35"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
       <c r="E26" s="22" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H26" s="22" t="s">
-        <v>64</v>
+        <v>82</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>69</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
@@ -5006,25 +6182,27 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="22" t="s">
-        <v>65</v>
+      <c r="B27" s="45"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="21" t="s">
+        <v>59</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="J27" s="10"/>
+        <v>127</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>130</v>
+      </c>
       <c r="K27" s="10"/>
       <c r="L27" s="10" t="str">
         <f t="shared" si="3"/>
@@ -5036,27 +6214,25 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="35"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="41"/>
       <c r="E28" s="21" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="21" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>144</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="J28" s="10"/>
       <c r="K28" s="10"/>
       <c r="L28" s="10" t="str">
         <f t="shared" si="3"/>
@@ -5068,132 +6244,138 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>138</v>
+      <c r="B29" s="45"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F29" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="H29" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="I29" s="38" t="s">
+        <v>126</v>
       </c>
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10" t="str">
+        <f>IF(B29="",L28,B29)</f>
+        <v>인게임기능</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="36"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="G30" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="H30" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="I30" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36" t="str">
         <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="20">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10" t="str">
-        <f>IF(B30="",L29,B30)</f>
-        <v>인게임기능</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="20">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10" t="str">
+    <row r="31" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="36"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="F31" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="H31" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36" t="str">
         <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A32" s="20">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="G32" s="10" t="s">
+    <row r="32" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="36"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="F32" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="I32" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10" t="str">
-        <f t="shared" si="3"/>
+      <c r="G32" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="H32" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="I32" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="36" t="str">
+        <f>IF(B32="",L30,B32)</f>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A33" s="20">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="I33" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10" t="str">
-        <f t="shared" si="3"/>
+    <row r="33" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A33" s="36"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="G33" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="H33" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="I33" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J33" s="36"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="36" t="str">
+        <f>IF(B33="",L30,B33)</f>
         <v>인게임기능</v>
       </c>
     </row>
@@ -5202,113 +6384,112 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="46"/>
-      <c r="E34" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>138</v>
+      <c r="B34" s="45"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="H34" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="I34" s="38" t="s">
+        <v>126</v>
       </c>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
-      <c r="L34" s="10" t="str">
-        <f t="shared" si="3"/>
+      <c r="L34" s="36" t="str">
+        <f>IF(B34="",L31,B34)</f>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A35" s="20">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B35" s="40"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="G35" s="10" t="s">
+    <row r="35" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="36"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="F35" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="G35" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="H35" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="I35" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="H35" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10" t="str">
-        <f t="shared" si="3"/>
+      <c r="J35" s="36"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="36" t="str">
+        <f>IF(B35="",L32,B35)</f>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A36" s="20">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="40"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="46"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="42" t="s">
+        <v>86</v>
+      </c>
       <c r="E36" s="21" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
       <c r="L36" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(B36="",L34,B36)</f>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A37" s="20">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" s="40"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="46"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="43"/>
       <c r="E37" s="21" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
@@ -5322,23 +6503,23 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="40"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="46"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="43"/>
       <c r="E38" s="21" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="F38" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="H38" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="G38" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H38" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="I38" s="19" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
@@ -5347,41 +6528,59 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="27" x14ac:dyDescent="0.2">
       <c r="A39" s="20">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" s="40"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="19"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>126</v>
+      </c>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10" t="str">
-        <f>IF(B39="",L34,B39)</f>
+        <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
       <c r="A40" s="20">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B40" s="40"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="19"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>126</v>
+      </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10" t="str">
@@ -5389,19 +6588,29 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="27" x14ac:dyDescent="0.2">
       <c r="A41" s="20">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" s="40"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="19"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="I41" s="19" t="s">
+        <v>126</v>
+      </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10" t="str">
@@ -5409,19 +6618,29 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="27" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="40"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="40"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="19"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="I42" s="19" t="s">
+        <v>126</v>
+      </c>
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
       <c r="L42" s="10" t="str">
@@ -5429,131 +6648,181 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="20">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10" t="str">
+    <row r="43" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A43" s="36"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="F43" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="H43" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="I43" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J43" s="36"/>
+      <c r="K43" s="36"/>
+      <c r="L43" s="36" t="str">
         <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="20">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B44" s="40"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E44" s="38"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10" t="str">
+    <row r="44" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+      <c r="A44" s="36"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="F44" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="G44" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="H44" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="I44" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="36" t="str">
         <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" s="20">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B45" s="40"/>
-      <c r="C45" s="40"/>
-      <c r="D45" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="E45" s="40"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10" t="str">
+    <row r="45" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+      <c r="A45" s="36"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="F45" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="G45" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="H45" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="I45" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="J45" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="K45" s="36"/>
+      <c r="L45" s="36" t="str">
         <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="20">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B46" s="40"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10" t="str">
-        <f t="shared" si="3"/>
+    <row r="46" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="36"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G46" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="H46" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="I46" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="J46" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="K46" s="36"/>
+      <c r="L46" s="36" t="str">
+        <f>IF(B46="",L39,B46)</f>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A47" s="20">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B47" s="40"/>
-      <c r="C47" s="40"/>
-      <c r="D47" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10" t="str">
-        <f t="shared" si="3"/>
+    <row r="47" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A47" s="36"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="F47" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="G47" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="H47" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="I47" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="36" t="str">
+        <f>IF(B47="",L40,B47)</f>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="20">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B48" s="40"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10" t="str">
-        <f t="shared" si="3"/>
+    <row r="48" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+      <c r="A48" s="36"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="F48" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G48" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="H48" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="I48" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J48" s="36"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="36" t="str">
+        <f>IF(B48="",L42,B48)</f>
         <v>인게임기능</v>
       </c>
     </row>
@@ -5562,37 +6831,205 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49" s="40"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="36"/>
+      <c r="L49" s="10"/>
+    </row>
+    <row r="50" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="20">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B50" s="45"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+    </row>
+    <row r="51" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="20">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B51" s="45"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+    </row>
+    <row r="52" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="20">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B52" s="45"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+    </row>
+    <row r="53" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A53" s="20">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B53" s="45"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="20">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B54" s="45"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="E54" s="47"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A55" s="20">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B55" s="45"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="45"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+    </row>
+    <row r="56" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A56" s="20">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B56" s="45"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+    </row>
+    <row r="57" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A57" s="20">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B57" s="45"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="10"/>
+    </row>
+    <row r="58" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A58" s="20">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B58" s="45"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="23"/>
+    </row>
+    <row r="59" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="23"/>
+      <c r="K59" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="C17:C39"/>
-    <mergeCell ref="D32:D39"/>
-    <mergeCell ref="B8:B16"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="C3:C7"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="C8:C16"/>
-    <mergeCell ref="B17:B49"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="C40:C49"/>
-    <mergeCell ref="D40:D43"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="D17:D24"/>
+  <mergeCells count="36">
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C16:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D29:D35"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:G6"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="J5:J6"/>
@@ -5601,158 +7038,315 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="H5:H6"/>
-    <mergeCell ref="D25:D29"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="D36:D42"/>
+    <mergeCell ref="B8:B15"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="C8:C15"/>
+    <mergeCell ref="B16:B58"/>
+    <mergeCell ref="C49:C58"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D16:D23"/>
+    <mergeCell ref="D24:D28"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1">
-    <cfRule type="containsBlanks" dxfId="39" priority="49">
+    <cfRule type="containsBlanks" dxfId="81" priority="115">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="52" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="80" priority="118" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="56" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="79" priority="122" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="60" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="78" priority="126" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="64" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="77" priority="130" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="68" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="76" priority="134" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(A1))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="containsText" dxfId="33" priority="55" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="75" priority="121" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="59" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="74" priority="125" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="63" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="73" priority="129" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="67" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="72" priority="133" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I3 I5 I30:I31 I39:I48 I7">
-    <cfRule type="containsBlanks" dxfId="29" priority="50">
+  <conditionalFormatting sqref="I1:I3 I5 I51:I58 I7:I14 I36:I43">
+    <cfRule type="containsBlanks" dxfId="71" priority="116">
       <formula>LEN(TRIM(I1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="69" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="70" priority="135" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(I1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3 I5 I30:I31 I39:I48 I7">
-    <cfRule type="containsText" dxfId="27" priority="53" operator="containsText" text="Pass">
+  <conditionalFormatting sqref="I2:I3 I5 I51:I58 I7:I14 I36:I43">
+    <cfRule type="containsText" dxfId="69" priority="119" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="57" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="68" priority="123" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="61" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="67" priority="127" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="65" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="66" priority="131" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I2))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="containsBlanks" dxfId="23" priority="51">
+    <cfRule type="containsBlanks" dxfId="65" priority="117">
       <formula>LEN(TRIM(J1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="54" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="64" priority="120" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="58" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="63" priority="124" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="62" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="62" priority="128" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="66" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="61" priority="132" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="70" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="60" priority="136" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(J1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32:I38">
+  <conditionalFormatting sqref="I16:I28">
+    <cfRule type="containsBlanks" dxfId="59" priority="73">
+      <formula>LEN(TRIM(I16))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="58" priority="78" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16:I28">
+    <cfRule type="containsText" dxfId="57" priority="74" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I16))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="56" priority="75" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I16))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="55" priority="76" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I16))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="77" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I50">
+    <cfRule type="containsBlanks" dxfId="53" priority="55">
+      <formula>LEN(TRIM(I50))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="52" priority="60" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I50))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I50">
+    <cfRule type="containsText" dxfId="51" priority="56" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I50))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="50" priority="57" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I50))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="49" priority="58" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I50))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="48" priority="59" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I50))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I49">
+    <cfRule type="containsBlanks" dxfId="47" priority="49">
+      <formula>LEN(TRIM(I49))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="46" priority="54" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I49))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I49">
+    <cfRule type="containsText" dxfId="45" priority="50" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I49))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="44" priority="51" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I49))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="43" priority="52" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I49))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="42" priority="53" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I49))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I46:I47">
+    <cfRule type="containsBlanks" dxfId="41" priority="43">
+      <formula>LEN(TRIM(I46))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="48" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I46))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I46:I47">
+    <cfRule type="containsText" dxfId="39" priority="44" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I46))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="38" priority="45" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I46))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="46" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I46))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="47" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I46))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
+    <cfRule type="containsBlanks" dxfId="35" priority="37">
+      <formula>LEN(TRIM(I15))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="42" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
+    <cfRule type="containsText" dxfId="33" priority="38" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I15))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="32" priority="39" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I15))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="40" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I15))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="41" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29:I31">
+    <cfRule type="containsBlanks" dxfId="29" priority="25">
+      <formula>LEN(TRIM(I29))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I29:I31">
+    <cfRule type="containsText" dxfId="27" priority="26" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I29))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="26" priority="27" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I29))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="28" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I29))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="29" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I29))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32">
+    <cfRule type="containsBlanks" dxfId="23" priority="19">
+      <formula>LEN(TRIM(I32))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32">
+    <cfRule type="containsText" dxfId="21" priority="20" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="21" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="22" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I32))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I32))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I33:I35">
     <cfRule type="containsBlanks" dxfId="17" priority="13">
-      <formula>LEN(TRIM(I32))=0</formula>
+      <formula>LEN(TRIM(I33))=0</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I32))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I33))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32:I38">
+  <conditionalFormatting sqref="I33:I35">
     <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I32))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I33))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I32))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I33))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I32))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I33))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I32))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I33))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I17:I29">
+  <conditionalFormatting sqref="I48">
     <cfRule type="containsBlanks" dxfId="11" priority="7">
-      <formula>LEN(TRIM(I17))=0</formula>
+      <formula>LEN(TRIM(I48))=0</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I17))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I48))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I17:I29">
+  <conditionalFormatting sqref="I48">
     <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I17))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I48))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I17))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I48))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I17))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I48))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I17))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I48))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8:I16">
+  <conditionalFormatting sqref="I44:I45">
     <cfRule type="containsBlanks" dxfId="5" priority="1">
-      <formula>LEN(TRIM(I8))=0</formula>
+      <formula>LEN(TRIM(I44))=0</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I8))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I44))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8:I16">
+  <conditionalFormatting sqref="I44:I45">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I8))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I44))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I8))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I44))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I8))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I44))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I8))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I44))))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5860,11 +7454,11 @@
       </c>
       <c r="B4" s="4">
         <f>COUNTIF(TestCase!L:L,A4)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5">
         <f t="shared" si="0"/>
-        <v>0.19148936170212766</v>
+        <v>0.1702127659574468</v>
       </c>
       <c r="D4" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;D$2&amp;"*",TestCase!$L:$L,$A4)</f>
@@ -5872,7 +7466,7 @@
       </c>
       <c r="E4" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;E$2&amp;"*",TestCase!$L:$L,$A4)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;F$2&amp;"*",TestCase!$L:$L,$A4)</f>
@@ -5888,7 +7482,7 @@
       </c>
       <c r="I4" s="6">
         <f t="shared" ref="I4:I5" si="1">SUM(D4:H4)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" ref="J4:J5" si="2">I4/B4</f>
@@ -5901,19 +7495,19 @@
       </c>
       <c r="B5" s="4">
         <f>COUNTIF(TestCase!L:L,A5)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="5">
         <f t="shared" si="0"/>
-        <v>0.68085106382978722</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="D5" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;D$2&amp;"*",TestCase!$L:$L,$A5)</f>
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E5" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;E$2&amp;"*",TestCase!$L:$L,$A5)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;F$2&amp;"*",TestCase!$L:$L,$A5)</f>
@@ -5929,11 +7523,11 @@
       </c>
       <c r="I5" s="6">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="2"/>
-        <v>0.625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5950,11 +7544,11 @@
       </c>
       <c r="D6" s="6">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="3"/>
@@ -5970,7 +7564,7 @@
       </c>
       <c r="I6" s="6">
         <f>SUM(I3:I5)</f>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="J6" s="6"/>
     </row>
@@ -5982,11 +7576,11 @@
       <c r="C7" s="8"/>
       <c r="D7" s="7">
         <f t="shared" ref="D7:I7" si="4">D6/$B6</f>
-        <v>0.53191489361702127</v>
+        <v>0.76595744680851063</v>
       </c>
       <c r="E7" s="7">
         <f t="shared" si="4"/>
-        <v>8.5106382978723402E-2</v>
+        <v>0.10638297872340426</v>
       </c>
       <c r="F7" s="7">
         <f t="shared" si="4"/>
@@ -6002,7 +7596,7 @@
       </c>
       <c r="I7" s="7">
         <f t="shared" si="4"/>
-        <v>0.61702127659574468</v>
+        <v>0.87234042553191493</v>
       </c>
       <c r="J7" s="6"/>
     </row>

--- a/QA/LC_TestCase.xlsx
+++ b/QA/LC_TestCase.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\전체\학교 과제\2-2학기\LC QA 문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\1027\QA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61383EA-1638-428E-9AF2-6B7935362986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC0E57F-FF4B-4BC1-99E4-823388E3B9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCase" sheetId="1" r:id="rId1"/>
@@ -281,7 +281,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="215">
   <si>
     <t>No</t>
   </si>
@@ -2368,43 +2368,7 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>퀘스트</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>플레이어 이동 관련</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">UI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>관련 보완</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Verdana"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>필요</t>
-    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -3686,6 +3650,336 @@
   </si>
   <si>
     <t>호감도가 일정 수치에 도달하면 플레이어에게 귀속된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>W(앞으로가기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>) 를 누른다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1. 게임을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 진행
+2.  W키를 입력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞으로 가진다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pass</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뒤로가기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>) 를 누른다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 진행
+2.  S키를 입력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒤로 가진다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왼쪽으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>) 를 누른다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 진행
+2.  A키를 입력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼쪽으로 가진다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 진행
+2.  D키를 입력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른쪽으로 가진다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>스페이스바(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>점프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>) 를 누른다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 진행
+2.  스페이스바 키를 입력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>점프가 된다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>W를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 누르는 중 Shift</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Verdana"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>달리기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>) 를 누른다</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>게임을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 진행
+2.  W키 입력중 Shift키를 입력</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도가 빨라진다</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오른쪽으로가기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="돋움"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>) 를 누른다</t>
+    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -3693,7 +3987,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3825,6 +4119,12 @@
       <sz val="9"/>
       <name val="돋움"/>
       <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -3973,7 +4273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4097,13 +4397,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4115,16 +4418,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4133,44 +4451,164 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="82">
+  <dxfs count="94">
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9900FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEFEFEF"/>
+          <bgColor rgb="FFEFEFEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE5CD"/>
+          <bgColor rgb="FFFCE5CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9900FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D2E9"/>
+          <bgColor rgb="FFD9D2E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCFE2F3"/>
+          <bgColor rgb="FFCFE2F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEFEFEF"/>
+          <bgColor rgb="FFEFEFEF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3F3F3"/>
+          <bgColor rgb="FFF3F3F3"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF9900"/>
@@ -5367,8 +5805,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L65"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -5384,7 +5822,7 @@
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -5422,9 +5860,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="10">
-        <f t="shared" ref="A2:A58" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A64" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="48" t="s">
@@ -5456,115 +5894,115 @@
         <v>게임실행</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="12.75" customHeight="1">
       <c r="A3" s="20">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="47" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47" t="s">
+      <c r="F3" s="49"/>
+      <c r="G3" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="H3" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
       <c r="L3" s="10" t="str">
         <f t="shared" si="1"/>
         <v>게임실행</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12">
       <c r="A4" s="20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
       <c r="L4" s="10" t="str">
         <f t="shared" si="1"/>
         <v>게임실행</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="12.75" customHeight="1">
       <c r="A5" s="20">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="47" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47" t="s">
+      <c r="F5" s="49"/>
+      <c r="G5" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="I5" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
       <c r="L5" s="10" t="str">
         <f t="shared" si="1"/>
         <v>게임실행</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" s="20">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
       <c r="L6" s="10" t="str">
         <f t="shared" si="1"/>
         <v>게임실행</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="12.75" customHeight="1" thickBot="1">
       <c r="A7" s="20">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="12" t="s">
         <v>22</v>
       </c>
@@ -5588,19 +6026,19 @@
         <v>게임실행</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" s="20">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>176</v>
+      <c r="C8" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>174</v>
       </c>
       <c r="E8" s="29" t="s">
         <v>87</v>
@@ -5624,14 +6062,14 @@
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" s="20">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="56"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="60"/>
       <c r="E9" s="21" t="s">
         <v>88</v>
       </c>
@@ -5654,14 +6092,14 @@
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" s="20">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="56"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="60"/>
       <c r="E10" s="21" t="s">
         <v>89</v>
       </c>
@@ -5684,15 +6122,15 @@
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="12.75" customHeight="1">
       <c r="A11" s="20">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="42" t="s">
-        <v>177</v>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="53" t="s">
+        <v>175</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>98</v>
@@ -5701,7 +6139,7 @@
         <v>115</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>99</v>
@@ -5716,14 +6154,14 @@
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="A12" s="20">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
       <c r="E12" s="10" t="s">
         <v>97</v>
       </c>
@@ -5746,14 +6184,14 @@
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="33.75">
       <c r="A13" s="20">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="59" t="s">
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="65" t="s">
         <v>96</v>
       </c>
       <c r="E13" s="37" t="s">
@@ -5763,10 +6201,10 @@
         <v>129</v>
       </c>
       <c r="G13" s="36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I13" s="38" t="s">
         <v>127</v>
@@ -5780,14 +6218,14 @@
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="22.5">
       <c r="A14" s="20">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="59"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="65"/>
       <c r="E14" s="39" t="s">
         <v>103</v>
       </c>
@@ -5795,7 +6233,7 @@
         <v>116</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H14" s="39" t="s">
         <v>106</v>
@@ -5810,11 +6248,11 @@
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="23.25" thickBot="1">
       <c r="A15" s="36"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="63"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="66"/>
       <c r="E15" s="31" t="s">
         <v>104</v>
       </c>
@@ -5822,7 +6260,7 @@
         <v>116</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>105</v>
@@ -5837,18 +6275,18 @@
         <v>메뉴기능</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="A16" s="20">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="54" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="25" t="s">
@@ -5873,14 +6311,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12">
       <c r="A17" s="20">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="42"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="53"/>
       <c r="E17" s="22" t="s">
         <v>50</v>
       </c>
@@ -5899,18 +6337,18 @@
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10" t="str">
-        <f t="shared" ref="L17:L45" si="3">IF(B17="",L16,B17)</f>
+        <f t="shared" ref="L17:L51" si="3">IF(B17="",L16,B17)</f>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12">
       <c r="A18" s="20">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="42"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="53"/>
       <c r="E18" s="22" t="s">
         <v>54</v>
       </c>
@@ -5933,14 +6371,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="22.5">
       <c r="A19" s="20">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="42"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="53"/>
       <c r="E19" s="22" t="s">
         <v>53</v>
       </c>
@@ -5963,14 +6401,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="22.5">
       <c r="A20" s="20">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="47"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="42"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="53"/>
       <c r="E20" s="21" t="s">
         <v>45</v>
       </c>
@@ -5993,14 +6431,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="22.5">
       <c r="A21" s="20">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="42"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="53"/>
       <c r="E21" s="21" t="s">
         <v>47</v>
       </c>
@@ -6023,14 +6461,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="22.5">
       <c r="A22" s="20">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="42"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="53"/>
       <c r="E22" s="21" t="s">
         <v>48</v>
       </c>
@@ -6053,14 +6491,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="22.5">
       <c r="A23" s="20">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="42"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="53"/>
       <c r="E23" s="21" t="s">
         <v>56</v>
       </c>
@@ -6085,14 +6523,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="A24" s="20">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="45"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="53" t="s">
+      <c r="B24" s="46"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="55" t="s">
         <v>60</v>
       </c>
       <c r="E24" s="21" t="s">
@@ -6117,14 +6555,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" s="20">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
       <c r="E25" s="22" t="s">
         <v>63</v>
       </c>
@@ -6147,14 +6585,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="22.5">
       <c r="A26" s="20">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
       <c r="E26" s="22" t="s">
         <v>65</v>
       </c>
@@ -6177,14 +6615,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="22.5">
       <c r="A27" s="20">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
       <c r="E27" s="21" t="s">
         <v>59</v>
       </c>
@@ -6209,14 +6647,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="22.5">
       <c r="A28" s="20">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="41"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="54"/>
       <c r="E28" s="21" t="s">
         <v>67</v>
       </c>
@@ -6239,27 +6677,27 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="22.5">
       <c r="A29" s="20">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="45"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="53" t="s">
+      <c r="B29" s="46"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="55" t="s">
         <v>85</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F29" s="36" t="s">
         <v>114</v>
       </c>
       <c r="G29" s="36" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H29" s="39" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I29" s="38" t="s">
         <v>126</v>
@@ -6271,22 +6709,22 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="33.75">
       <c r="A30" s="36"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
       <c r="E30" s="37" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F30" s="36" t="s">
         <v>114</v>
       </c>
       <c r="G30" s="36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I30" s="38" t="s">
         <v>126</v>
@@ -6298,22 +6736,22 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="33.75">
       <c r="A31" s="36"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="54"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
       <c r="E31" s="37" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F31" s="36" t="s">
         <v>114</v>
       </c>
       <c r="G31" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="H31" s="39" t="s">
         <v>153</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>155</v>
       </c>
       <c r="I31" s="38" t="s">
         <v>126</v>
@@ -6325,22 +6763,22 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="33.75">
       <c r="A32" s="36"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="54"/>
-      <c r="D32" s="54"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
       <c r="E32" s="37" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F32" s="36" t="s">
         <v>114</v>
       </c>
       <c r="G32" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="H32" s="39" t="s">
         <v>154</v>
-      </c>
-      <c r="H32" s="39" t="s">
-        <v>156</v>
       </c>
       <c r="I32" s="38" t="s">
         <v>126</v>
@@ -6352,22 +6790,22 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="22.5">
       <c r="A33" s="36"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
       <c r="E33" s="37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G33" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" s="39" t="s">
         <v>173</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>175</v>
       </c>
       <c r="I33" s="38" t="s">
         <v>126</v>
@@ -6379,25 +6817,25 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="22.5">
       <c r="A34" s="20">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
       <c r="E34" s="37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F34" s="36" t="s">
         <v>114</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H34" s="39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I34" s="38" t="s">
         <v>126</v>
@@ -6409,22 +6847,22 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12">
       <c r="A35" s="36"/>
-      <c r="B35" s="45"/>
-      <c r="C35" s="54"/>
-      <c r="D35" s="41"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="54"/>
       <c r="E35" s="39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H35" s="39" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I35" s="38" t="s">
         <v>126</v>
@@ -6436,14 +6874,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12">
       <c r="A36" s="20">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="42" t="s">
+      <c r="B36" s="46"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="53" t="s">
         <v>86</v>
       </c>
       <c r="E36" s="21" t="s">
@@ -6453,7 +6891,7 @@
         <v>113</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H36" s="21" t="s">
         <v>109</v>
@@ -6468,14 +6906,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12">
       <c r="A37" s="20">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" s="45"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="43"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="64"/>
       <c r="E37" s="21" t="s">
         <v>108</v>
       </c>
@@ -6483,7 +6921,7 @@
         <v>113</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H37" s="21" t="s">
         <v>110</v>
@@ -6498,14 +6936,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="22.5">
       <c r="A38" s="20">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="45"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="43"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="64"/>
       <c r="E38" s="21" t="s">
         <v>111</v>
       </c>
@@ -6513,7 +6951,7 @@
         <v>113</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H38" s="21" t="s">
         <v>121</v>
@@ -6528,14 +6966,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="22.5">
       <c r="A39" s="20">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" s="45"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="43"/>
+      <c r="B39" s="46"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="64"/>
       <c r="E39" s="21" t="s">
         <v>112</v>
       </c>
@@ -6543,7 +6981,7 @@
         <v>113</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H39" s="21" t="s">
         <v>120</v>
@@ -6558,14 +6996,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="67.5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="56.25">
       <c r="A40" s="20">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="54"/>
-      <c r="D40" s="43"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="64"/>
       <c r="E40" s="21" t="s">
         <v>117</v>
       </c>
@@ -6573,7 +7011,7 @@
         <v>113</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H40" s="21" t="s">
         <v>122</v>
@@ -6588,14 +7026,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="22.5">
       <c r="A41" s="20">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" s="45"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="43"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="64"/>
       <c r="E41" s="21" t="s">
         <v>118</v>
       </c>
@@ -6603,7 +7041,7 @@
         <v>113</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H41" s="21" t="s">
         <v>123</v>
@@ -6618,14 +7056,14 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="22.5">
       <c r="A42" s="20">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="45"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="43"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="64"/>
       <c r="E42" s="21" t="s">
         <v>119</v>
       </c>
@@ -6633,7 +7071,7 @@
         <v>113</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H42" s="21" t="s">
         <v>124</v>
@@ -6648,24 +7086,24 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="27" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="22.5">
       <c r="A43" s="36"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="54"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="56"/>
       <c r="D43" s="34" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E43" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="F43" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="H43" s="39" t="s">
         <v>192</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="G43" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="H43" s="39" t="s">
-        <v>194</v>
       </c>
       <c r="I43" s="38" t="s">
         <v>126</v>
@@ -6677,307 +7115,361 @@
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="36"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="54"/>
-      <c r="D44" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="E44" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="F44" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="G44" s="36" t="s">
-        <v>170</v>
-      </c>
-      <c r="H44" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="I44" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="36" t="str">
+    <row r="44" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A44" s="41"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="H44" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="I44" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="J44" s="41"/>
+      <c r="K44" s="41"/>
+      <c r="L44" s="41" t="str">
         <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
-      <c r="A45" s="36"/>
-      <c r="B45" s="45"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="F45" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="G45" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="H45" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="I45" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="J45" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="K45" s="36"/>
-      <c r="L45" s="36" t="str">
+    <row r="45" spans="1:12" ht="23.25">
+      <c r="A45" s="41"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="F45" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G45" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="H45" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="I45" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41"/>
+      <c r="L45" s="41" t="str">
         <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="40.5" x14ac:dyDescent="0.2">
-      <c r="A46" s="36"/>
-      <c r="B46" s="45"/>
-      <c r="C46" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="D46" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="E46" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="F46" s="25" t="s">
+    <row r="46" spans="1:12" ht="23.25">
+      <c r="A46" s="41"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F46" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="G46" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="H46" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="I46" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="J46" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="K46" s="36"/>
-      <c r="L46" s="36" t="str">
-        <f>IF(B46="",L39,B46)</f>
+      <c r="G46" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="H46" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="I46" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="J46" s="41"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="41" t="str">
+        <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A47" s="36"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="E47" s="39" t="s">
-        <v>188</v>
+    <row r="47" spans="1:12" ht="23.25">
+      <c r="A47" s="41"/>
+      <c r="B47" s="46"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="41" t="s">
+        <v>214</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="G47" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="H47" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="I47" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
-      <c r="L47" s="36" t="str">
-        <f>IF(B47="",L40,B47)</f>
+        <v>133</v>
+      </c>
+      <c r="G47" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="H47" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="I47" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="J47" s="41"/>
+      <c r="K47" s="41"/>
+      <c r="L47" s="41" t="str">
+        <f t="shared" si="3"/>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="27" x14ac:dyDescent="0.2">
-      <c r="A48" s="36"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="41"/>
-      <c r="D48" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="E48" s="39" t="s">
-        <v>179</v>
+    <row r="48" spans="1:12" ht="23.25">
+      <c r="A48" s="41"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="41" t="s">
+        <v>208</v>
       </c>
       <c r="F48" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="G48" s="36" t="s">
+      <c r="G48" s="41" t="s">
+        <v>209</v>
+      </c>
+      <c r="H48" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="I48" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="J48" s="41"/>
+      <c r="K48" s="41"/>
+      <c r="L48" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v>인게임기능</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="23.25">
+      <c r="A49" s="41"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G49" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="H49" s="44" t="s">
+        <v>213</v>
+      </c>
+      <c r="I49" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v>인게임기능</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="33.75">
+      <c r="A50" s="36"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="H48" s="39" t="s">
+      <c r="F50" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="G50" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="I50" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v>인게임기능</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="33.75">
+      <c r="A51" s="36"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="I48" s="38" t="s">
+      <c r="F51" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="G51" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="H51" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="I51" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="J51" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="K51" s="36"/>
+      <c r="L51" s="36" t="str">
+        <f t="shared" si="3"/>
+        <v>인게임기능</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="33.75">
+      <c r="A52" s="36"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E52" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="F52" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G52" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="H52" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="I52" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="J52" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="K52" s="36"/>
+      <c r="L52" s="36" t="str">
+        <f>IF(B52="",L39,B52)</f>
+        <v>인게임기능</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="22.5">
+      <c r="A53" s="36"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="G53" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="H53" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="I53" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="36" t="str">
-        <f>IF(B48="",L42,B48)</f>
+      <c r="J53" s="36"/>
+      <c r="K53" s="36"/>
+      <c r="L53" s="36" t="str">
+        <f>IF(B53="",L40,B53)</f>
         <v>인게임기능</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A49" s="20">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="60"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="39"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="36"/>
-      <c r="L49" s="10"/>
+    <row r="54" spans="1:12" ht="22.5">
+      <c r="A54" s="36"/>
+      <c r="B54" s="46"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="F54" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G54" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="H54" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="I54" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J54" s="36"/>
+      <c r="K54" s="36"/>
+      <c r="L54" s="36" t="str">
+        <f>IF(B54="",L42,B54)</f>
+        <v>인게임기능</v>
+      </c>
     </row>
-    <row r="50" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="20">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="57"/>
-      <c r="E50" s="39"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="39"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="36"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-    </row>
-    <row r="51" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="20">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="58" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-    </row>
-    <row r="52" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="20">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-    </row>
-    <row r="53" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A53" s="20">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A54" s="20">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="E54" s="47"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12">
       <c r="A55" s="20">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="39"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="36"/>
+      <c r="K55" s="36"/>
       <c r="L55" s="10"/>
     </row>
-    <row r="56" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12">
       <c r="A56" s="20">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B56" s="45"/>
-      <c r="C56" s="45"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="10"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="36"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
     </row>
-    <row r="57" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="12.75" customHeight="1">
       <c r="A57" s="20">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="45"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="21" t="s">
-        <v>139</v>
-      </c>
+      <c r="B57" s="46"/>
+      <c r="C57" s="46"/>
+      <c r="D57" s="61"/>
       <c r="E57" s="10"/>
       <c r="F57" s="10"/>
       <c r="G57" s="10"/>
@@ -6987,14 +7479,14 @@
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
     </row>
-    <row r="58" spans="1:12" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="12.75" customHeight="1">
       <c r="A58" s="20">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="45"/>
-      <c r="C58" s="45"/>
-      <c r="D58" s="21"/>
+      <c r="B58" s="46"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="62"/>
       <c r="E58" s="10"/>
       <c r="F58" s="10"/>
       <c r="G58" s="10"/>
@@ -7002,34 +7494,127 @@
       <c r="I58" s="19"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
-      <c r="L58" s="23"/>
+      <c r="L58" s="10"/>
     </row>
-    <row r="59" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="24"/>
-      <c r="J59" s="23"/>
-      <c r="K59" s="23"/>
+    <row r="59" spans="1:12">
+      <c r="A59" s="20">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B59" s="46"/>
+      <c r="C59" s="46"/>
+      <c r="D59" s="55"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="41"/>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="A60" s="20">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="10"/>
+      <c r="L60" s="41"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="A61" s="20">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B61" s="46"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="41"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="20">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B62" s="46"/>
+      <c r="C62" s="46"/>
+      <c r="D62" s="56"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="42"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="41"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="20">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B63" s="46"/>
+      <c r="C63" s="46"/>
+      <c r="D63" s="56"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="41"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="10"/>
+      <c r="K63" s="10"/>
+      <c r="L63" s="41"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="20">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B64" s="46"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="10"/>
+      <c r="K64" s="10"/>
+      <c r="L64" s="41"/>
+    </row>
+    <row r="65" spans="5:11" ht="12.75" customHeight="1">
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="23"/>
+      <c r="H65" s="23"/>
+      <c r="I65" s="24"/>
+      <c r="J65" s="23"/>
+      <c r="K65" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C16:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D29:D35"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E3:E4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="J5:J6"/>
@@ -7038,296 +7623,349 @@
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="H5:H6"/>
+    <mergeCell ref="B16:B64"/>
+    <mergeCell ref="C55:C64"/>
+    <mergeCell ref="D16:D23"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="D59:D64"/>
+    <mergeCell ref="D44:D49"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="D55:D56"/>
     <mergeCell ref="D36:D42"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="C16:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D29:D35"/>
     <mergeCell ref="B8:B15"/>
-    <mergeCell ref="E54:E55"/>
     <mergeCell ref="B2:B7"/>
     <mergeCell ref="C3:C7"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="C8:C15"/>
-    <mergeCell ref="B16:B58"/>
-    <mergeCell ref="C49:C58"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="D16:D23"/>
-    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D13:D15"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1">
-    <cfRule type="containsBlanks" dxfId="81" priority="115">
+    <cfRule type="containsBlanks" dxfId="93" priority="127">
       <formula>LEN(TRIM(A1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="118" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="92" priority="130" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="79" priority="122" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="91" priority="134" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="126" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="90" priority="138" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="77" priority="130" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="89" priority="142" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="134" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="88" priority="146" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(A1))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="containsText" dxfId="75" priority="121" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="87" priority="133" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="125" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="86" priority="137" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="73" priority="129" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="85" priority="141" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="133" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="84" priority="145" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I3 I5 I51:I58 I7:I14 I36:I43">
-    <cfRule type="containsBlanks" dxfId="71" priority="116">
+  <conditionalFormatting sqref="I1:I3 I5 I57:I58 I7:I14 I36:I43">
+    <cfRule type="containsBlanks" dxfId="83" priority="128">
       <formula>LEN(TRIM(I1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="135" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="82" priority="147" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(I1))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I3 I5 I51:I58 I7:I14 I36:I43">
-    <cfRule type="containsText" dxfId="69" priority="119" operator="containsText" text="Pass">
+  <conditionalFormatting sqref="I2:I3 I5 I57:I58 I7:I14 I36:I43">
+    <cfRule type="containsText" dxfId="81" priority="131" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="123" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="80" priority="135" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="67" priority="127" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="79" priority="139" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I2))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="131" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="78" priority="143" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I2))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="containsBlanks" dxfId="65" priority="117">
+    <cfRule type="containsBlanks" dxfId="77" priority="129">
       <formula>LEN(TRIM(J1))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="120" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="76" priority="132" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="124" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="75" priority="136" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="128" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="74" priority="140" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="61" priority="132" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="73" priority="144" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(J1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="136" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="72" priority="148" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(J1))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I28">
-    <cfRule type="containsBlanks" dxfId="59" priority="73">
+    <cfRule type="containsBlanks" dxfId="71" priority="85">
       <formula>LEN(TRIM(I16))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="78" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="70" priority="90" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(I16))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:I28">
-    <cfRule type="containsText" dxfId="57" priority="74" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="69" priority="86" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="75" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="68" priority="87" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="76" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="67" priority="88" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I16))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="77" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="66" priority="89" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I16))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I50">
+  <conditionalFormatting sqref="I56">
+    <cfRule type="containsBlanks" dxfId="65" priority="67">
+      <formula>LEN(TRIM(I56))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="64" priority="72" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I56))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I56">
+    <cfRule type="containsText" dxfId="63" priority="68" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I56))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="62" priority="69" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I56))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="61" priority="70" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I56))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="60" priority="71" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I56))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I55">
+    <cfRule type="containsBlanks" dxfId="59" priority="61">
+      <formula>LEN(TRIM(I55))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="58" priority="66" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I55))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I55">
+    <cfRule type="containsText" dxfId="57" priority="62" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I55))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="56" priority="63" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I55))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="55" priority="64" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I55))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="54" priority="65" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I55))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I52:I53">
     <cfRule type="containsBlanks" dxfId="53" priority="55">
-      <formula>LEN(TRIM(I50))=0</formula>
+      <formula>LEN(TRIM(I52))=0</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="52" priority="60" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I50))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I52))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I50">
+  <conditionalFormatting sqref="I52:I53">
     <cfRule type="containsText" dxfId="51" priority="56" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I50))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I52))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="50" priority="57" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I50))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I52))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="49" priority="58" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I50))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I52))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="48" priority="59" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I50))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I49">
-    <cfRule type="containsBlanks" dxfId="47" priority="49">
-      <formula>LEN(TRIM(I49))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="54" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I49))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I49">
-    <cfRule type="containsText" dxfId="45" priority="50" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I49))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="51" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I49))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="52" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I49))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="53" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I49))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I46:I47">
-    <cfRule type="containsBlanks" dxfId="41" priority="43">
-      <formula>LEN(TRIM(I46))=0</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="48" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I46))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I46:I47">
-    <cfRule type="containsText" dxfId="39" priority="44" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I46))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="45" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I46))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="46" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I46))))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="47" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I46))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I52))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsBlanks" dxfId="35" priority="37">
+    <cfRule type="containsBlanks" dxfId="47" priority="49">
       <formula>LEN(TRIM(I15))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="42" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="46" priority="54" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(I15))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="33" priority="38" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="45" priority="50" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="39" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="44" priority="51" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="40" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="43" priority="52" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I15))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="41" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="42" priority="53" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I15))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29:I31">
-    <cfRule type="containsBlanks" dxfId="29" priority="25">
+    <cfRule type="containsBlanks" dxfId="41" priority="37">
       <formula>LEN(TRIM(I29))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="40" priority="42" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(I29))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29:I31">
-    <cfRule type="containsText" dxfId="27" priority="26" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="39" priority="38" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I29))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="27" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="38" priority="39" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I29))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="28" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="37" priority="40" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I29))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="29" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="36" priority="41" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I29))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32">
-    <cfRule type="containsBlanks" dxfId="23" priority="19">
+    <cfRule type="containsBlanks" dxfId="35" priority="31">
       <formula>LEN(TRIM(I32))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="34" priority="36" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(I32))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32">
-    <cfRule type="containsText" dxfId="21" priority="20" operator="containsText" text="Pass">
+    <cfRule type="containsText" dxfId="33" priority="32" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="21" operator="containsText" text="Fail">
+    <cfRule type="containsText" dxfId="32" priority="33" operator="containsText" text="Fail">
       <formula>NOT(ISERROR(SEARCH(("Fail"),(I32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="22" operator="containsText" text="Block">
+    <cfRule type="containsText" dxfId="31" priority="34" operator="containsText" text="Block">
       <formula>NOT(ISERROR(SEARCH(("Block"),(I32))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="N/A">
+    <cfRule type="containsText" dxfId="30" priority="35" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH(("N/A"),(I32))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33:I35">
-    <cfRule type="containsBlanks" dxfId="17" priority="13">
+    <cfRule type="containsBlanks" dxfId="29" priority="25">
       <formula>LEN(TRIM(I33))=0</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="N/T">
+    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="N/T">
       <formula>NOT(ISERROR(SEARCH(("N/T"),(I33))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33:I35">
+    <cfRule type="containsText" dxfId="27" priority="26" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="26" priority="27" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="28" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I33))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="29" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I33))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I54">
+    <cfRule type="containsBlanks" dxfId="23" priority="19">
+      <formula>LEN(TRIM(I54))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I54))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I54">
+    <cfRule type="containsText" dxfId="21" priority="20" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I54))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="21" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I54))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="22" operator="containsText" text="Block">
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I54))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I54))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I50:I51">
+    <cfRule type="containsBlanks" dxfId="17" priority="13">
+      <formula>LEN(TRIM(I50))=0</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="N/T">
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I50))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I50:I51">
     <cfRule type="containsText" dxfId="15" priority="14" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I33))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I50))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="14" priority="15" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I33))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I50))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="13" priority="16" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I33))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I50))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="12" priority="17" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I33))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I50))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I48">
+  <conditionalFormatting sqref="I59:I64">
     <cfRule type="containsBlanks" dxfId="11" priority="7">
-      <formula>LEN(TRIM(I48))=0</formula>
+      <formula>LEN(TRIM(I59))=0</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="N/T">
-      <formula>NOT(ISERROR(SEARCH(("N/T"),(I48))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/T"),(I59))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I48">
+  <conditionalFormatting sqref="I59:I64">
     <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="Pass">
-      <formula>NOT(ISERROR(SEARCH(("Pass"),(I48))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Pass"),(I59))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="Fail">
-      <formula>NOT(ISERROR(SEARCH(("Fail"),(I48))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Fail"),(I59))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="Block">
-      <formula>NOT(ISERROR(SEARCH(("Block"),(I48))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("Block"),(I59))))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH(("N/A"),(I48))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("N/A"),(I59))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I44:I45">
+  <conditionalFormatting sqref="I44:I49">
     <cfRule type="containsBlanks" dxfId="5" priority="1">
       <formula>LEN(TRIM(I44))=0</formula>
     </cfRule>
@@ -7335,7 +7973,7 @@
       <formula>NOT(ISERROR(SEARCH(("N/T"),(I44))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I44:I45">
+  <conditionalFormatting sqref="I44:I49">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH(("Pass"),(I44))))</formula>
     </cfRule>
@@ -7361,7 +7999,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" customWidth="1"/>
@@ -7370,12 +8008,12 @@
     <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="12.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="12.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -7407,7 +8045,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="12.75" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -7417,7 +8055,7 @@
       </c>
       <c r="C3" s="5">
         <f t="shared" ref="C3:C5" si="0">IFERROR(B3/$B$6,0)</f>
-        <v>0.1276595744680851</v>
+        <v>0.11320754716981132</v>
       </c>
       <c r="D3" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;D$2&amp;"*",TestCase!$L:$L,$A3)</f>
@@ -7448,7 +8086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="12.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -7458,7 +8096,7 @@
       </c>
       <c r="C4" s="5">
         <f t="shared" si="0"/>
-        <v>0.1702127659574468</v>
+        <v>0.15094339622641509</v>
       </c>
       <c r="D4" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;D$2&amp;"*",TestCase!$L:$L,$A4)</f>
@@ -7489,21 +8127,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="4">
         <f>COUNTIF(TestCase!L:L,A5)</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C5" s="5">
         <f t="shared" si="0"/>
-        <v>0.7021276595744681</v>
+        <v>0.73584905660377353</v>
       </c>
       <c r="D5" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;D$2&amp;"*",TestCase!$L:$L,$A5)</f>
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4">
         <f>COUNTIFS(TestCase!$I:$I,"*"&amp;E$2&amp;"*",TestCase!$L:$L,$A5)</f>
@@ -7523,20 +8161,20 @@
       </c>
       <c r="I5" s="6">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J5" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="12.75" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="8">
         <f t="shared" ref="B6:H6" si="3">SUM(B3:B5)</f>
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C6" s="9">
         <f>SUM(C3:C5)</f>
@@ -7544,7 +8182,7 @@
       </c>
       <c r="D6" s="6">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" si="3"/>
@@ -7564,11 +8202,11 @@
       </c>
       <c r="I6" s="6">
         <f>SUM(I3:I5)</f>
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="12.75" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>30</v>
       </c>
@@ -7576,11 +8214,11 @@
       <c r="C7" s="8"/>
       <c r="D7" s="7">
         <f t="shared" ref="D7:I7" si="4">D6/$B6</f>
-        <v>0.76595744680851063</v>
+        <v>0.79245283018867929</v>
       </c>
       <c r="E7" s="7">
         <f t="shared" si="4"/>
-        <v>0.10638297872340426</v>
+        <v>9.4339622641509441E-2</v>
       </c>
       <c r="F7" s="7">
         <f t="shared" si="4"/>
@@ -7592,11 +8230,11 @@
       </c>
       <c r="H7" s="7">
         <f t="shared" si="4"/>
-        <v>8.5106382978723402E-2</v>
+        <v>7.5471698113207544E-2</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" si="4"/>
-        <v>0.87234042553191493</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="J7" s="6"/>
     </row>
